--- a/data/trans_orig/P34B02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de días a la semana que la población realiza gimnasia suave juegos que requieren poco esfuerzo y similares</t>
+          <t>Número medio de días a la semana que, durante más de 30 minutos, la población realiza gimnasia suave como juegos que requieren poco esfuerzo y similares (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,32 +677,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,34</t>
+          <t>0,18; 0,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,41</t>
+          <t>0,22; 0,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,87</t>
+          <t>0,55; 0,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,22</t>
+          <t>0,1; 0,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,3</t>
+          <t>0,14; 0,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 0,71</t>
+          <t>0,51; 0,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,73</t>
+          <t>0,56; 0,76</t>
         </is>
       </c>
     </row>
@@ -792,17 +792,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,58</t>
+          <t>0,38; 0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,02</t>
+          <t>0,37; 1,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,28</t>
+          <t>0,15; 0,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -812,17 +812,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,84</t>
+          <t>0,64; 0,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,3</t>
+          <t>0,21; 0,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,48</t>
+          <t>0,35; 0,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,43</t>
+          <t>0,27; 0,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,46</t>
+          <t>0,28; 0,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,19</t>
+          <t>0,83; 1,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,35</t>
+          <t>0,21; 0,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,63</t>
+          <t>0,21; 0,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,37</t>
+          <t>0,26; 0,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,84</t>
+          <t>0,44; 0,82</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,84</t>
+          <t>0,59; 0,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,37; 0,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1127,27 +1127,27 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,99</t>
+          <t>0,7; 0,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,19; 0,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,34</t>
+          <t>0,27; 0,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,7</t>
+          <t>0,53; 0,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,3</t>
+          <t>0,24; 0,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,82</t>
+          <t>0,66; 0,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34B02-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34B02-Habitat-trans_orig.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,36</t>
+          <t>0,19; 0,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,17 +687,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,87</t>
+          <t>0,54; 0,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,21</t>
+          <t>0,11; 0,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,29</t>
+          <t>0,15; 0,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,26</t>
+          <t>0,16; 0,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,31</t>
+          <t>0,2; 0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,76</t>
+          <t>0,56; 0,73</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,84</t>
         </is>
       </c>
     </row>
@@ -787,27 +787,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,37</t>
+          <t>0,22; 0,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,57</t>
+          <t>0,39; 0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,02</t>
+          <t>0,81; 1,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,28</t>
+          <t>0,15; 0,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,42</t>
+          <t>0,27; 0,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,3</t>
+          <t>0,2; 0,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,87</t>
+          <t>0,76; 0,92</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,42</t>
+          <t>0,26; 0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,16</t>
+          <t>0,81; 1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,35</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,63</t>
+          <t>0,51; 0,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,82</t>
+          <t>0,7; 0,88</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,95</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,48</t>
+          <t>0,3; 0,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,62</t>
+          <t>0,43; 0,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,28</t>
+          <t>1,01; 1,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,42</t>
+          <t>0,27; 0,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,85</t>
+          <t>0,72; 0,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,39</t>
+          <t>0,27; 0,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,48</t>
+          <t>0,36; 0,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,0</t>
+          <t>0,88; 1,04</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -1122,27 +1122,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,47</t>
+          <t>0,38; 0,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 0,98</t>
+          <t>0,88; 1,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,26</t>
+          <t>0,18; 0,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,34</t>
+          <t>0,26; 0,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,7</t>
+          <t>0,65; 0,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 0,83</t>
+          <t>0,78; 0,86</t>
         </is>
       </c>
     </row>
